--- a/Result/checksun_type/廣播電視_電影產業.xlsx
+++ b/Result/checksun_type/廣播電視_電影產業.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,21 +1057,17 @@
           <t>17.75</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>17.76</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AM2" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>17.66</v>
+      </c>
+      <c r="AO2" t="inlineStr">
         <is>
           <t>17.66</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>17.66</t>
-        </is>
-      </c>
       <c r="AP2" t="inlineStr">
         <is>
           <t>-25.13</t>
@@ -1112,20 +1108,16 @@
           <t>739197.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>759897.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>759897.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>755275.3</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>761471.04</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>761471.04</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-15279.07344219415</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>739197</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>739197.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>17.73</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>17.77</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>17.66</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>17.77</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>17.66</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>990766.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>657168.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>657168.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>807612.1</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>754906.1</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>754906.1</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-12290.6290516553</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>990766</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>990766.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>17.69</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>17.76</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>17.66</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>17.66</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>540721.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>639642.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>639642</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>990113.0</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>742640.94</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>742640.9399999999</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-34536.29317046935</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>540721</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>540721.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>17.72</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>17.76</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>17.67</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>17.67</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>1315703.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>583174.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>583174</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>989294.2</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>772643.56</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>772643.5600000001</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-16863.2671555439</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>1315703</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>1315703.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>17.82</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>17.78</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>17.68</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>17.78</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>17.68</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>213100.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>633140.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>633140.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>872640.7</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>772503.7</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>772503.7</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-74047.61330723844</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>213100</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>213100.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>17.88</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>17.78</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>17.7</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>17.78</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>17.7</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>225551.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>750653.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>750653.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>895870.7</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>771690.9</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>771690.9</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-34958.94304868625</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>225551</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>225551.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>17.96</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>17.78</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>17.7</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>17.78</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>17.7</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>903135.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>958056.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>958056</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>926851.3</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>781155.08</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>781155.08</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>20796.51242955576</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>903135</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>903135.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>18.04</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>17.8</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>17.72</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>17.72</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>258381.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>1340584.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>1340584</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>894410.1</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>792758.98</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>792758.98</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>27106.14481170301</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>258381</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>258381.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>18.03</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>17.79</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>17.73</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>17.79</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>17.73</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>1565535.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>1395414.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>1395414.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>906912.2</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>846389.72</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>846389.72</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>104232.6144714954</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>1565535</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>1565535.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>17.97</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>17.76</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>17.73</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>17.73</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>800664.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>1112141.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>1112141</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>790768.9</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>840761.12</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>840761.12</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>70638.47775435983</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>800664</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>800664.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>17.88</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>17.72</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>17.73</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>17.72</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>17.73</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>1262565.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>1041088.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>1041088.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>847618.4</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>846759.92</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>846759.92</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>102074.5153815104</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>1262565</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>1262565.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>75.98</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>75.85</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>78.08</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>75.84999999999999</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>78.08</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>1114576.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>1301037.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>1301037</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>1154908.7</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>1388957.8</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>1388957.8</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-30993.3900636069</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>1114576</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>1114576.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>75.5</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>75.82</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>78.15</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>75.81999999999999</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>78.15000000000001</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>1857981.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>1401471.0</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>1401471</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>1223486.9</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>1382298.96</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>1382298.96</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-17960.27243426954</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>1857981</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>1857981.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>75.5</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>75.82</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>78.24</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>75.81999999999999</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>78.23999999999999</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>1150358.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>1088277.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>1088277.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>1117573.8</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>1374461.06</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>1374461.06</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-78350.63037684932</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>1150358</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>1150358.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>75.38000000000001</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>75.82</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>78.33</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>75.81999999999999</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>78.33</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>1900637.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>941115.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>941115</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>1239892.7</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>1371770.7</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>1371770.7</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-86007.58349564718</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>1900637</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>1900637.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>75.4</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>75.9</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>78.41</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>78.41</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>481633.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>659846.8</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>659846.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>1112084.1</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>1355308.78</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>1355308.78</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-174261.4242547996</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>481633</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>481633.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>75.64</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>76.04</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>78.53</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>76.04000000000001</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>78.53</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>1616746.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>1008780.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>1008780.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>1189930.2</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>1353441.62</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>1353441.62</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-142078.5744730602</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>1616746</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>1616746.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>76.02</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>76.23</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>78.65</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>76.23</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>78.65000000000001</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>292015.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>1045502.8</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>1045502.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>1175306.0</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>1339186.58</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>1339186.58</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-212648.0899822519</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>292015</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>292015.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>75.97999999999999</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>76.31</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>78.74</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>76.31</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>78.73999999999999</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>414544.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>1146869.8</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>1146869.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>1309107.2</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>1377752.38</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>1377752.38</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-163931.6446388736</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>414544</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>414544.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>75.96</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>76.54</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>78.84</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>76.54000000000001</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>78.84</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>494296.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>1538670.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>1538670.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>1405606.8</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>1384609.08</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>1384609.08</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-101610.1282683739</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>494296</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>494296.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>75.94</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>76.74</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>78.93</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>76.73999999999999</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>78.93000000000001</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>2226301.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>1564321.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>1564321.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>1400549.5</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>1391213.28</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>1391213.28</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-17495.31458664616</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>2226301</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>2226301.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>76.0</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>76.94</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>79.03</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>76.94</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>79.03</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>1800358.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>1371080.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>1371080</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>1284013.1</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>1366058.46</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>1366058.46</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-82278.42666322645</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>1800358</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>1800358.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>226.1</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>235.1</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>239.53</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>235.1</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>239.53</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>87560295.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>90409131.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>90409131.59999999</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>93926577.0</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>91142940.14</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>91142940.14</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-3023499.791926354</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>87560295</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>87560295.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>226.4</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>235.15</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>239.77</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>235.15</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>239.77</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>96574195.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>83666332.6</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>83666332.59999999</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>103194422.3</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>91481493.92</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>91481493.92</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-2766856.581867665</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>96574195</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>96574195.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>228.2</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>235.5</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>240.24</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>235.5</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>240.24</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>71644075.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>83897394.0</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>83897394</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>101865765.6</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>91508752.72</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>91508752.72</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-3267182.118145689</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>71644075</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>71644075.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>230.4</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>235.8</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>240.65</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>235.8</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>240.65</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>123805914.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>89321740.0</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>89321740</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>105919275.1</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>91810212.38</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>91810212.38</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-1194163.522894815</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>123805914</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>123805914.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>234.5</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>236.28</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>241.22</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>236.28</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>241.22</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>72461179.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>88104747.2</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>88104747.2</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>113492473.6</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>90562774.2</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>90562774.2</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-3778828.153861612</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>72461179</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>72461179.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>236.8</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>236.65</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>241.75</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>236.65</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>241.75</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>53846300.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>97444022.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>97444022.40000001</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>127286983.3</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>89517261.66</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>89517261.66</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-1835026.44260481</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>53846300</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>53846300.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>238.7</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>236.9</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>242.22</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>236.9</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>242.22</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>97729502.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>122722512.0</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>122722512</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>126605734.2</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>88915651.56</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>88915651.56</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>3001821.124997914</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>97729502</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>97729502.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>240.3</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>237.08</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>242.65</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>237.08</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>242.65</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>98765805.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>119834137.2</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>119834137.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>123032675.2</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>87410611.56</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>87410611.56</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>5102623.824251875</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>98765805</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>98765805.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>241.0</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>236.95</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>242.95</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>236.95</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>242.95</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>117720950.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>122516810.2</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>122516810.2</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>120087218.2</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>86170263.86</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>86170263.86</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>7810501.508034274</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>117720950</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>117720950.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>241.3</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>236.62</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>243.04</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>236.62</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>243.04</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>119157555.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>138880200.0</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>138880200</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>115721500.5</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>85084091.88</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>85084091.88</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>9369043.323865041</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>119157555</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>119157555.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>242.9</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>236.58</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>243.3</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>236.58</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>243.3</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>180238748.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>157129944.2</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>157129944.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>112511739.2</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>84766716.06</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>84766716.06</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>11107000.97777095</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>180238748</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>180238748.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>57.76000000000001</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>57.54</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>54.47</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>57.54</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>54.47</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>58.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>252.6</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>252.6</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>0</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-82.85489821189958</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>58</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>58.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>58.1</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>57.46</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>54.4</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>57.46</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>54.4</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>132.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>299.2</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>299.2</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>0</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-69.69525090339852</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>132</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>58.58000000000001</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>57.4</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>54.37</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>54.37</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>403.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>0</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>0</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-56.33521007327556</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>403</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>403.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>58.5</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>57.22</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>54.29</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>54.29</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>552.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>0</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>0</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-64.27317995619728</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>552</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>552.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>57.98</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>56.9</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>54.19</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>54.19</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>118.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>0</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>0</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-89.28195193336404</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>118</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>118.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>57.38</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>56.54</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>54.08</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>56.54</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>54.08</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>291.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>0</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>0</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-75.32012790312513</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>291</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>291.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>56.62</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>56.22</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>53.98</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>56.22</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>53.98</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>0</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>0</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-66.91975283082633</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>0</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>56.58000000000001</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>55.91</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>53.9</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>55.91</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>53.9</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>175.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>0</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>0</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-66.91975283082633</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>175</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>175.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>56.64</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>55.57</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>53.79</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>55.57</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>53.79</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>0</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>0</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-33.36868258238928</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>0</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>57.14</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>55.35</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>55.35</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>53.7</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>62.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>396.4</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>396.4</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>929.9</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>398.84</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>398.84</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-33.36868258238928</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>62</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>62.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>57.94</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>55.12</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>53.67</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>55.12</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>53.67</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>354.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>562.0</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>562</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>950.1</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>404.02</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>404.02</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>15.88228378974236</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>354</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>354.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>46.67999999999999</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>47.88</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>48.87</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>47.88</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>48.87</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>2109129.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>2458297.6</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>2458297.6</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>5078193.8</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>6629823.02</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>6629823.02</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-754610.5354381707</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>2109129</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>2109129.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>46.52</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>47.97</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>48.93</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>47.97</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>48.93</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>3037237.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>2620310.2</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>2620310.2</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>5453187.1</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>6784633.74</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>6784633.74</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-652482.3483004505</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>3037237</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>3037237.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>46.48</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>48.09</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>49.01</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>48.09</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>49.01</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>2143660.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>4430189.4</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>4430189.4</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>6330010.5</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>6913540.0</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>6913540</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-582722.1399501208</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>2143660</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>2143660.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>46.47</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>48.2</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>49.09</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>49.09</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>2791542.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>7076648.0</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>7076648</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>6887614.7</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>7011326.84</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>7011326.84</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-366512.8015942881</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>2791542</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>2791542.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>46.79</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>48.33</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>49.18</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>48.33</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>49.18</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>2209920.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>7508206.2</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>7508206.2</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>6865024.4</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>7078517.18</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>7078517.18</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-113968.5038861595</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>2209920</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>2209920.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>47.09</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>48.46</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>49.26</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>48.46</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>49.26</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>2919192.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>7698090.0</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>7698090</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>7188670.5</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>7183450.56</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>7183450.56</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>313196.0108356727</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>2919192</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>2919192.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>47.43</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>48.57</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>49.34</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>48.57</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>49.34</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>12086633.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>8286064.0</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>8286064</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>7520804.1</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>7362422.94</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>7362422.94</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>836252.0314798728</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>12086633</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>12086633.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>47.77</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>48.67</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>49.43</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>48.67</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>49.43</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>15375953.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>8229831.6</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>8229831.6</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>6792981.4</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>7237931.14</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>7237931.14</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>571382.9527044492</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>15375953</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>15375953.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>48.22</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>48.76</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>49.51</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>48.76</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>49.51</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>4949333.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>6698581.4</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>6698581.4</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>6052146.9</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>7260196.36</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>7260196.36</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-179835.1224284563</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>4949333</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>4949333.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>48.37</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>48.8</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>49.58</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>49.58</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>3159339.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>6221842.6</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>6221842.6</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>5828296.7</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>7356213.14</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>7356213.14</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-129443.26110302</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>3159339</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>3159339.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>48.48</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>48.82</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>49.64</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>48.82</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>49.64</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>5859062.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>6679251.0</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>6679251</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>5848455.2</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>7392404.04</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>7392404.04</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>138953.1572584258</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>5859062</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>5859062.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>19.81</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>20.57</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>21.13</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>20.57</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>21.13</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>39.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>261.2</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>261.2</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>440.8</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>939.44</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>939.4400000000001</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-77.1984147045531</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>39</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>39.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>20.08</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>20.65</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>21.16</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>21.16</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>178.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>488.0</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>488</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>467.3</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>947.7</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>947.7</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-56.26310290734688</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>178</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>178.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>20.28</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>20.76</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>21.2</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>20.76</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>21.2</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>220.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>563.0</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>563</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>491.6</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>948.4</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>948.4</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-39.23897523607559</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>220</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>220.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>20.42</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>20.84</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>21.23</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>21.23</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>335.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>625.6</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>625.6</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>504.6</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>962.98</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>962.98</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-18.01740087582812</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>335</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>335.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>20.57</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>20.94</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>21.26</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>20.94</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>21.26</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>534.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>621.4</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>621.4</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>507.9</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>962.58</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>962.58</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>0.6211839558050087</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>534</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>534.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>20.71</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>21.02</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>21.27</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>21.27</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>1173.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>620.4</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>620.4</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>481.8</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>962.56</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>962.5599999999999</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>5.904120002573563</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>1173</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>1173.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>20.76</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>21.08</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>21.25</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>21.08</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>21.25</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>553.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>446.6</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>446.6</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>388.2</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>949.6</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>949.6</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-55.22397564499198</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>553</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>553.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>20.84</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>21.16</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>21.24</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>21.16</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>21.24</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>533.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>420.2</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>420.2</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>376.4</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>945.04</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>945.04</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-74.14897029705008</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>533</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>533.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>20.81</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>21.24</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>21.22</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>21.24</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>21.22</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>314.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>383.6</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>383.6</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>336.1</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>946.32</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>946.3200000000001</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-96.39364228938132</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>314</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>314.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>20.78</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>21.37</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>21.21</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>21.37</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>21.21</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>529.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>394.4</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>394.4</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>332.3</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>949.96</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>949.96</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-101.2648293395194</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>529</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>529.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>20.7</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>21.54</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>21.2</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>21.54</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>21.2</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>304.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>343.2</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>343.2</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>307.1</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>958.3</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>958.3</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-127.6427812204482</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>304</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>304.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>10.47</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>13.09</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>12.01</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>12.01</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>12.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>814.2</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>814.2</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>785.0</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>265.58</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>265.58</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>56.89545144131273</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>12</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>10.89</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>13.34</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>11.97</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>13.34</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>11.97</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>448.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>1106.6</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>1106.6</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>786.8</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>267.88</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>267.88</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>131.2436423707534</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>448</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>448.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>11.54</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>13.6</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>11.92</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>11.92</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>462.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>1113.8</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>1113.8</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>753.8</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>259.14</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>259.14</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>186.0537850424274</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>462</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>462.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>12.27</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>13.83</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>11.88</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>11.88</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>2194.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>1144.6</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>1144.6</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>739.7</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>249.96</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>249.96</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>256.2092108218751</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>2194</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>2194.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>12.92</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>14.02</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>11.83</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>11.83</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>955.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>806.2</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>806.2</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>522.0</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>215.7</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>215.7</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>161.7094901203047</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>955</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>955.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>13.41</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>14.16</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>11.76</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>11.76</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>1474.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>755.8</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>755.8</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>434.2</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>205.32</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>205.32</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>153.6845501851934</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>1474</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>1474.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>13.95</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>14.27</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>11.69</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>11.69</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>484.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>467.0</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>467</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>294.9</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>178.48</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>178.48</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>81.12447348556316</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>484</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>484.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>14.25</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>14.33</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>11.59</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>11.59</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>616.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>393.8</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>393.8</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>255.5</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>171.14</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>171.14</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>80.6413470044642</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>616</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>616.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>14.47</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>14.38</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>11.48</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>11.48</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>502.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>334.8</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>334.8</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>200.8</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>160.12</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>160.12</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>62.92826106702051</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>502</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>502.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>14.5</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>14.44</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>11.36</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>11.36</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>703.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>237.8</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>237.8</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>160.3</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>156.74</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>156.74</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>47.59070040399308</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>703</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>703.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>14.49</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>14.52</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>11.25</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>11.25</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>30.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>112.6</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>112.6</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>91.7</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>144.42</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>144.42</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>2.444517299525572</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>30</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>48.32</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>49.46</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>55.04</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>55.04</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>289324693.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>359053739.8</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>359053739.8</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>779219302.6</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>1233289107.3</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>1233289107.3</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>-90860825.19125909</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>289324693</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>289324693.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>48.31</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>49.57</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>55.39</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>49.57</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>55.39</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>298587633.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>427404646.6</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>427404646.6</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>788465115.2</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>1336844077.5</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>1336844077.5</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>-80434512.81531477</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>298587633</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>298587633.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>48.41</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>49.77</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>55.78</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>49.77</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>55.78</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>302147334.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>549695262.2</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>549695262.2</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>789932410.0</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>1388106125.2</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>1388106125.2</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>-63659577.53484738</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>302147334</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>302147334.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>49.14</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>56.17</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>56.17</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>429086972.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>664802561.8</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>664802561.8</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>805598718.5</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>1482928219.1</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>1482928219.1</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>-37803224.47222078</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>429086972</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>429086972.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>49.73999999999999</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>50.18</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>56.62</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>50.18</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>56.62</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>476122067.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>751503060.6</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>751503060.6</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>853426202.9</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>1565117969.24</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>1565117969.24</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>-13116137.5801748</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>476122067</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>476122067.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>50.16</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>50.38</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>57.1</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>50.38</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>57.1</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>631079227.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>1199384865.4</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>1199384865.4</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>852262787.8</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>1647059956.98</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>1647059956.98</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>17580088.42918277</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>631079227</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>631079227.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>50.69</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>50.56</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>57.56</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>50.56</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>57.56</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>910040711.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>1149525583.8</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>1149525583.8</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>840320195.5</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>1776903570.96</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>1776903570.96</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>44201426.71293712</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>910040711</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>910040711.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>50.32</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>50.72</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>58.07</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>50.72</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>58.07</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>877683832.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>1030169557.8</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>1030169557.8</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>806899222.5</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>1957468999.34</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>1957468999.34</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>50764557.16426682</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>877683832</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>877683832.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>49.52</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>50.73</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>58.46</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>50.73</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>58.46</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>862589466.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>946394875.2</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>946394875.2</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>771003853.8</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>2163437979.1</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>2163437979.1</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>61794246.37458563</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>862589466</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>862589466.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>48.86</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>50.84</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>50.84</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>58.9</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>2715531091.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>955349345.2</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>955349345.2</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>721647627.7</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>2402549153.18</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>2402549153.18</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>76961261.37594843</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>2715531091</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>2715531091.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>48.84</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>50.98</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>59.29</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>50.98</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>59.29</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>381782819.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>505140710.2</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>505140710.2</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>501963719.2</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>2548936714.28</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>2548936714.28</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>-102649650.6355312</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>381782819</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>381782819.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
